--- a/Time to Fixation Experiments - Changing Chemotaxis Equation/Combined_Time_Fix_Data.xlsx
+++ b/Time to Fixation Experiments - Changing Chemotaxis Equation/Combined_Time_Fix_Data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Moar Documents\GitHub\Bac_Evol_SSA\Time to Fixation Experiments - Changing Chemotaxis Equation\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6061DCD7-950E-40E9-9C88-D284B00BF0AD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{237C5703-45D3-4B40-AC7D-C11063AFE222}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -478,6 +478,9 @@
       <c r="B2" t="s">
         <v>6</v>
       </c>
+      <c r="C2">
+        <v>16634</v>
+      </c>
       <c r="D2" t="s">
         <v>8</v>
       </c>
@@ -500,6 +503,9 @@
       </c>
       <c r="B3" t="s">
         <v>6</v>
+      </c>
+      <c r="C3">
+        <v>22472</v>
       </c>
       <c r="D3" t="s">
         <v>8</v>
@@ -524,6 +530,9 @@
       <c r="B4" t="s">
         <v>6</v>
       </c>
+      <c r="C4">
+        <v>15586</v>
+      </c>
       <c r="D4" t="s">
         <v>8</v>
       </c>
@@ -547,6 +556,9 @@
       <c r="B5" t="s">
         <v>6</v>
       </c>
+      <c r="C5">
+        <v>15735</v>
+      </c>
       <c r="D5" t="s">
         <v>8</v>
       </c>
@@ -570,6 +582,9 @@
       <c r="B6" t="s">
         <v>6</v>
       </c>
+      <c r="C6">
+        <v>15363</v>
+      </c>
       <c r="D6" t="s">
         <v>8</v>
       </c>
@@ -593,6 +608,9 @@
       <c r="B7" t="s">
         <v>6</v>
       </c>
+      <c r="C7">
+        <v>16444</v>
+      </c>
       <c r="D7" t="s">
         <v>8</v>
       </c>
@@ -616,6 +634,9 @@
       <c r="B8" t="s">
         <v>6</v>
       </c>
+      <c r="C8">
+        <v>16198</v>
+      </c>
       <c r="D8" t="s">
         <v>8</v>
       </c>
@@ -639,6 +660,9 @@
       <c r="B9" t="s">
         <v>6</v>
       </c>
+      <c r="C9">
+        <v>17846</v>
+      </c>
       <c r="D9" t="s">
         <v>8</v>
       </c>
@@ -662,6 +686,9 @@
       <c r="B10" t="s">
         <v>6</v>
       </c>
+      <c r="C10">
+        <v>15841</v>
+      </c>
       <c r="D10" t="s">
         <v>8</v>
       </c>
@@ -685,6 +712,9 @@
       <c r="B11" t="s">
         <v>6</v>
       </c>
+      <c r="C11">
+        <v>17363</v>
+      </c>
       <c r="D11" t="s">
         <v>8</v>
       </c>
@@ -707,6 +737,9 @@
       </c>
       <c r="B12" t="s">
         <v>6</v>
+      </c>
+      <c r="C12">
+        <v>14760</v>
       </c>
       <c r="D12" t="s">
         <v>8</v>
@@ -731,6 +764,9 @@
       <c r="B13" t="s">
         <v>6</v>
       </c>
+      <c r="C13">
+        <v>18310</v>
+      </c>
       <c r="D13" t="s">
         <v>8</v>
       </c>
@@ -754,6 +790,9 @@
       <c r="B14" t="s">
         <v>6</v>
       </c>
+      <c r="C14">
+        <v>14800</v>
+      </c>
       <c r="D14" t="s">
         <v>8</v>
       </c>
@@ -777,6 +816,9 @@
       <c r="B15" t="s">
         <v>6</v>
       </c>
+      <c r="C15">
+        <v>15814</v>
+      </c>
       <c r="D15" t="s">
         <v>8</v>
       </c>
@@ -800,6 +842,9 @@
       <c r="B16" t="s">
         <v>6</v>
       </c>
+      <c r="C16">
+        <v>18416</v>
+      </c>
       <c r="D16" t="s">
         <v>8</v>
       </c>
@@ -823,6 +868,9 @@
       <c r="B17" t="s">
         <v>6</v>
       </c>
+      <c r="C17">
+        <v>16894</v>
+      </c>
       <c r="D17" t="s">
         <v>8</v>
       </c>
@@ -846,6 +894,9 @@
       <c r="B18" t="s">
         <v>6</v>
       </c>
+      <c r="C18">
+        <v>23383</v>
+      </c>
       <c r="D18" t="s">
         <v>8</v>
       </c>
@@ -869,6 +920,9 @@
       <c r="B19" t="s">
         <v>6</v>
       </c>
+      <c r="C19">
+        <v>16284</v>
+      </c>
       <c r="D19" t="s">
         <v>8</v>
       </c>
@@ -892,6 +946,9 @@
       <c r="B20" t="s">
         <v>6</v>
       </c>
+      <c r="C20">
+        <v>20268</v>
+      </c>
       <c r="D20" t="s">
         <v>8</v>
       </c>
@@ -915,6 +972,9 @@
       <c r="B21" t="s">
         <v>6</v>
       </c>
+      <c r="C21">
+        <v>18299</v>
+      </c>
       <c r="D21" t="s">
         <v>8</v>
       </c>
@@ -938,6 +998,9 @@
       <c r="B22" t="s">
         <v>6</v>
       </c>
+      <c r="C22">
+        <v>15518</v>
+      </c>
       <c r="D22" t="s">
         <v>8</v>
       </c>
@@ -961,6 +1024,9 @@
       <c r="B23" t="s">
         <v>6</v>
       </c>
+      <c r="C23">
+        <v>18258</v>
+      </c>
       <c r="D23" t="s">
         <v>8</v>
       </c>
@@ -984,6 +1050,9 @@
       <c r="B24" t="s">
         <v>6</v>
       </c>
+      <c r="C24">
+        <v>14661</v>
+      </c>
       <c r="D24" t="s">
         <v>8</v>
       </c>
@@ -1007,6 +1076,9 @@
       <c r="B25" t="s">
         <v>6</v>
       </c>
+      <c r="C25">
+        <v>18435</v>
+      </c>
       <c r="D25" t="s">
         <v>8</v>
       </c>
@@ -1030,6 +1102,9 @@
       <c r="B26" t="s">
         <v>6</v>
       </c>
+      <c r="C26">
+        <v>15699</v>
+      </c>
       <c r="D26" t="s">
         <v>8</v>
       </c>
@@ -1053,6 +1128,9 @@
       <c r="B27" t="s">
         <v>6</v>
       </c>
+      <c r="C27">
+        <v>17490</v>
+      </c>
       <c r="D27" t="s">
         <v>8</v>
       </c>
@@ -1076,6 +1154,9 @@
       <c r="B28" t="s">
         <v>6</v>
       </c>
+      <c r="C28">
+        <v>17610</v>
+      </c>
       <c r="D28" t="s">
         <v>8</v>
       </c>
@@ -1099,6 +1180,9 @@
       <c r="B29" t="s">
         <v>6</v>
       </c>
+      <c r="C29">
+        <v>19275</v>
+      </c>
       <c r="D29" t="s">
         <v>8</v>
       </c>
@@ -1122,6 +1206,9 @@
       <c r="B30" t="s">
         <v>6</v>
       </c>
+      <c r="C30">
+        <v>15778</v>
+      </c>
       <c r="D30" t="s">
         <v>8</v>
       </c>
@@ -1145,6 +1232,9 @@
       <c r="B31" t="s">
         <v>6</v>
       </c>
+      <c r="C31">
+        <v>16835</v>
+      </c>
       <c r="D31" t="s">
         <v>8</v>
       </c>
@@ -1168,6 +1258,9 @@
       <c r="B32" t="s">
         <v>6</v>
       </c>
+      <c r="C32">
+        <v>17221</v>
+      </c>
       <c r="D32" t="s">
         <v>8</v>
       </c>
@@ -1191,6 +1284,9 @@
       <c r="B33" t="s">
         <v>6</v>
       </c>
+      <c r="C33">
+        <v>15998</v>
+      </c>
       <c r="D33" t="s">
         <v>8</v>
       </c>
@@ -1214,6 +1310,9 @@
       <c r="B34" t="s">
         <v>6</v>
       </c>
+      <c r="C34">
+        <v>15551</v>
+      </c>
       <c r="D34" t="s">
         <v>8</v>
       </c>
@@ -1237,6 +1336,9 @@
       <c r="B35" t="s">
         <v>6</v>
       </c>
+      <c r="C35">
+        <v>16320</v>
+      </c>
       <c r="D35" t="s">
         <v>8</v>
       </c>
@@ -1260,6 +1362,9 @@
       <c r="B36" t="s">
         <v>6</v>
       </c>
+      <c r="C36">
+        <v>17597</v>
+      </c>
       <c r="D36" t="s">
         <v>8</v>
       </c>
@@ -1283,6 +1388,9 @@
       <c r="B37" t="s">
         <v>6</v>
       </c>
+      <c r="C37">
+        <v>16577</v>
+      </c>
       <c r="D37" t="s">
         <v>8</v>
       </c>
@@ -1306,6 +1414,9 @@
       <c r="B38" t="s">
         <v>6</v>
       </c>
+      <c r="C38">
+        <v>17523</v>
+      </c>
       <c r="D38" t="s">
         <v>8</v>
       </c>
@@ -1329,6 +1440,9 @@
       <c r="B39" t="s">
         <v>6</v>
       </c>
+      <c r="C39">
+        <v>16864</v>
+      </c>
       <c r="D39" t="s">
         <v>8</v>
       </c>
@@ -1352,6 +1466,9 @@
       <c r="B40" t="s">
         <v>6</v>
       </c>
+      <c r="C40">
+        <v>17102</v>
+      </c>
       <c r="D40" t="s">
         <v>8</v>
       </c>
@@ -1375,6 +1492,9 @@
       <c r="B41" t="s">
         <v>6</v>
       </c>
+      <c r="C41">
+        <v>17282</v>
+      </c>
       <c r="D41" t="s">
         <v>8</v>
       </c>
@@ -1398,6 +1518,9 @@
       <c r="B42" t="s">
         <v>6</v>
       </c>
+      <c r="C42">
+        <v>16472</v>
+      </c>
       <c r="D42" t="s">
         <v>8</v>
       </c>
@@ -1421,6 +1544,9 @@
       <c r="B43" t="s">
         <v>6</v>
       </c>
+      <c r="C43">
+        <v>14526</v>
+      </c>
       <c r="D43" t="s">
         <v>8</v>
       </c>
@@ -1444,6 +1570,9 @@
       <c r="B44" t="s">
         <v>6</v>
       </c>
+      <c r="C44">
+        <v>16708</v>
+      </c>
       <c r="D44" t="s">
         <v>8</v>
       </c>
@@ -1467,6 +1596,9 @@
       <c r="B45" t="s">
         <v>6</v>
       </c>
+      <c r="C45">
+        <v>17392</v>
+      </c>
       <c r="D45" t="s">
         <v>8</v>
       </c>
@@ -1490,6 +1622,9 @@
       <c r="B46" t="s">
         <v>6</v>
       </c>
+      <c r="C46">
+        <v>18781</v>
+      </c>
       <c r="D46" t="s">
         <v>8</v>
       </c>
@@ -1513,6 +1648,9 @@
       <c r="B47" t="s">
         <v>6</v>
       </c>
+      <c r="C47">
+        <v>17353</v>
+      </c>
       <c r="D47" t="s">
         <v>8</v>
       </c>
@@ -1536,6 +1674,9 @@
       <c r="B48" t="s">
         <v>6</v>
       </c>
+      <c r="C48">
+        <v>19775</v>
+      </c>
       <c r="D48" t="s">
         <v>8</v>
       </c>
@@ -1559,6 +1700,9 @@
       <c r="B49" t="s">
         <v>6</v>
       </c>
+      <c r="C49">
+        <v>16158</v>
+      </c>
       <c r="D49" t="s">
         <v>8</v>
       </c>
@@ -1582,6 +1726,9 @@
       <c r="B50" t="s">
         <v>6</v>
       </c>
+      <c r="C50">
+        <v>15542</v>
+      </c>
       <c r="D50" t="s">
         <v>8</v>
       </c>
@@ -1605,6 +1752,9 @@
       <c r="B51" t="s">
         <v>6</v>
       </c>
+      <c r="C51">
+        <v>19375</v>
+      </c>
       <c r="D51" t="s">
         <v>8</v>
       </c>
@@ -1628,6 +1778,9 @@
       <c r="B52" t="s">
         <v>6</v>
       </c>
+      <c r="C52">
+        <v>16775</v>
+      </c>
       <c r="D52" t="s">
         <v>8</v>
       </c>
@@ -1651,6 +1804,9 @@
       <c r="B53" t="s">
         <v>6</v>
       </c>
+      <c r="C53">
+        <v>14966</v>
+      </c>
       <c r="D53" t="s">
         <v>8</v>
       </c>
@@ -1674,6 +1830,9 @@
       <c r="B54" t="s">
         <v>6</v>
       </c>
+      <c r="C54">
+        <v>18290</v>
+      </c>
       <c r="D54" t="s">
         <v>8</v>
       </c>
@@ -1697,6 +1856,9 @@
       <c r="B55" t="s">
         <v>6</v>
       </c>
+      <c r="C55">
+        <v>16439</v>
+      </c>
       <c r="D55" t="s">
         <v>8</v>
       </c>
@@ -1720,6 +1882,9 @@
       <c r="B56" t="s">
         <v>6</v>
       </c>
+      <c r="C56">
+        <v>16085</v>
+      </c>
       <c r="D56" t="s">
         <v>8</v>
       </c>
@@ -1743,6 +1908,9 @@
       <c r="B57" t="s">
         <v>6</v>
       </c>
+      <c r="C57">
+        <v>15109</v>
+      </c>
       <c r="D57" t="s">
         <v>8</v>
       </c>
@@ -1766,6 +1934,9 @@
       <c r="B58" t="s">
         <v>6</v>
       </c>
+      <c r="C58">
+        <v>16827</v>
+      </c>
       <c r="D58" t="s">
         <v>8</v>
       </c>
@@ -1789,6 +1960,9 @@
       <c r="B59" t="s">
         <v>6</v>
       </c>
+      <c r="C59">
+        <v>17459</v>
+      </c>
       <c r="D59" t="s">
         <v>8</v>
       </c>
@@ -1812,6 +1986,9 @@
       <c r="B60" t="s">
         <v>6</v>
       </c>
+      <c r="C60">
+        <v>16333</v>
+      </c>
       <c r="D60" t="s">
         <v>8</v>
       </c>
@@ -1835,6 +2012,9 @@
       <c r="B61" t="s">
         <v>6</v>
       </c>
+      <c r="C61">
+        <v>16709</v>
+      </c>
       <c r="D61" t="s">
         <v>8</v>
       </c>
@@ -1858,6 +2038,9 @@
       <c r="B62" t="s">
         <v>6</v>
       </c>
+      <c r="C62">
+        <v>17258</v>
+      </c>
       <c r="D62" t="s">
         <v>8</v>
       </c>
@@ -1881,6 +2064,9 @@
       <c r="B63" t="s">
         <v>6</v>
       </c>
+      <c r="C63">
+        <v>14761</v>
+      </c>
       <c r="D63" t="s">
         <v>8</v>
       </c>
@@ -1904,6 +2090,9 @@
       <c r="B64" t="s">
         <v>6</v>
       </c>
+      <c r="C64">
+        <v>16775</v>
+      </c>
       <c r="D64" t="s">
         <v>8</v>
       </c>
@@ -1927,6 +2116,9 @@
       <c r="B65" t="s">
         <v>6</v>
       </c>
+      <c r="C65">
+        <v>14020</v>
+      </c>
       <c r="D65" t="s">
         <v>8</v>
       </c>
@@ -1950,6 +2142,9 @@
       <c r="B66" t="s">
         <v>6</v>
       </c>
+      <c r="C66">
+        <v>16239</v>
+      </c>
       <c r="D66" t="s">
         <v>8</v>
       </c>
@@ -1973,6 +2168,9 @@
       <c r="B67" t="s">
         <v>6</v>
       </c>
+      <c r="C67">
+        <v>14369</v>
+      </c>
       <c r="D67" t="s">
         <v>8</v>
       </c>
@@ -1996,6 +2194,9 @@
       <c r="B68" t="s">
         <v>6</v>
       </c>
+      <c r="C68">
+        <v>17432</v>
+      </c>
       <c r="D68" t="s">
         <v>8</v>
       </c>
@@ -2019,6 +2220,9 @@
       <c r="B69" t="s">
         <v>6</v>
       </c>
+      <c r="C69">
+        <v>17718</v>
+      </c>
       <c r="D69" t="s">
         <v>8</v>
       </c>
@@ -2042,6 +2246,9 @@
       <c r="B70" t="s">
         <v>6</v>
       </c>
+      <c r="C70">
+        <v>15054</v>
+      </c>
       <c r="D70" t="s">
         <v>8</v>
       </c>
@@ -2065,6 +2272,9 @@
       <c r="B71" t="s">
         <v>6</v>
       </c>
+      <c r="C71">
+        <v>14690</v>
+      </c>
       <c r="D71" t="s">
         <v>8</v>
       </c>
@@ -2088,6 +2298,9 @@
       <c r="B72" t="s">
         <v>6</v>
       </c>
+      <c r="C72">
+        <v>18087</v>
+      </c>
       <c r="D72" t="s">
         <v>8</v>
       </c>
@@ -2111,6 +2324,9 @@
       <c r="B73" t="s">
         <v>6</v>
       </c>
+      <c r="C73">
+        <v>15455</v>
+      </c>
       <c r="D73" t="s">
         <v>8</v>
       </c>
@@ -2134,6 +2350,9 @@
       <c r="B74" t="s">
         <v>6</v>
       </c>
+      <c r="C74">
+        <v>17360</v>
+      </c>
       <c r="D74" t="s">
         <v>8</v>
       </c>
@@ -2157,6 +2376,9 @@
       <c r="B75" t="s">
         <v>6</v>
       </c>
+      <c r="C75">
+        <v>20873</v>
+      </c>
       <c r="D75" t="s">
         <v>8</v>
       </c>
@@ -2180,6 +2402,9 @@
       <c r="B76" t="s">
         <v>6</v>
       </c>
+      <c r="C76">
+        <v>17800</v>
+      </c>
       <c r="D76" t="s">
         <v>8</v>
       </c>
@@ -2203,6 +2428,9 @@
       <c r="B77" t="s">
         <v>6</v>
       </c>
+      <c r="C77">
+        <v>17082</v>
+      </c>
       <c r="D77" t="s">
         <v>8</v>
       </c>
@@ -2226,6 +2454,9 @@
       <c r="B78" t="s">
         <v>6</v>
       </c>
+      <c r="C78">
+        <v>17010</v>
+      </c>
       <c r="D78" t="s">
         <v>8</v>
       </c>
@@ -2249,6 +2480,9 @@
       <c r="B79" t="s">
         <v>6</v>
       </c>
+      <c r="C79">
+        <v>16223</v>
+      </c>
       <c r="D79" t="s">
         <v>8</v>
       </c>
@@ -2272,6 +2506,9 @@
       <c r="B80" t="s">
         <v>6</v>
       </c>
+      <c r="C80">
+        <v>20619</v>
+      </c>
       <c r="D80" t="s">
         <v>8</v>
       </c>
@@ -2295,6 +2532,9 @@
       <c r="B81" t="s">
         <v>6</v>
       </c>
+      <c r="C81">
+        <v>17068</v>
+      </c>
       <c r="D81" t="s">
         <v>8</v>
       </c>
@@ -2318,6 +2558,9 @@
       <c r="B82" t="s">
         <v>6</v>
       </c>
+      <c r="C82">
+        <v>18559</v>
+      </c>
       <c r="D82" t="s">
         <v>8</v>
       </c>
@@ -2341,6 +2584,9 @@
       <c r="B83" t="s">
         <v>6</v>
       </c>
+      <c r="C83">
+        <v>16719</v>
+      </c>
       <c r="D83" t="s">
         <v>8</v>
       </c>
@@ -2364,6 +2610,9 @@
       <c r="B84" t="s">
         <v>6</v>
       </c>
+      <c r="C84">
+        <v>18323</v>
+      </c>
       <c r="D84" t="s">
         <v>8</v>
       </c>
@@ -2387,6 +2636,9 @@
       <c r="B85" t="s">
         <v>6</v>
       </c>
+      <c r="C85">
+        <v>16893</v>
+      </c>
       <c r="D85" t="s">
         <v>8</v>
       </c>
@@ -2410,6 +2662,9 @@
       <c r="B86" t="s">
         <v>6</v>
       </c>
+      <c r="C86">
+        <v>19397</v>
+      </c>
       <c r="D86" t="s">
         <v>8</v>
       </c>
@@ -2433,6 +2688,9 @@
       <c r="B87" t="s">
         <v>6</v>
       </c>
+      <c r="C87">
+        <v>17573</v>
+      </c>
       <c r="D87" t="s">
         <v>8</v>
       </c>
@@ -2456,6 +2714,9 @@
       <c r="B88" t="s">
         <v>6</v>
       </c>
+      <c r="C88">
+        <v>16644</v>
+      </c>
       <c r="D88" t="s">
         <v>8</v>
       </c>
@@ -2479,6 +2740,9 @@
       <c r="B89" t="s">
         <v>6</v>
       </c>
+      <c r="C89">
+        <v>16510</v>
+      </c>
       <c r="D89" t="s">
         <v>8</v>
       </c>
@@ -2502,6 +2766,9 @@
       <c r="B90" t="s">
         <v>6</v>
       </c>
+      <c r="C90">
+        <v>17834</v>
+      </c>
       <c r="D90" t="s">
         <v>8</v>
       </c>
@@ -2525,6 +2792,9 @@
       <c r="B91" t="s">
         <v>6</v>
       </c>
+      <c r="C91">
+        <v>16340</v>
+      </c>
       <c r="D91" t="s">
         <v>8</v>
       </c>
@@ -2548,6 +2818,9 @@
       <c r="B92" t="s">
         <v>6</v>
       </c>
+      <c r="C92">
+        <v>17189</v>
+      </c>
       <c r="D92" t="s">
         <v>8</v>
       </c>
@@ -2571,6 +2844,9 @@
       <c r="B93" t="s">
         <v>6</v>
       </c>
+      <c r="C93">
+        <v>15984</v>
+      </c>
       <c r="D93" t="s">
         <v>8</v>
       </c>
@@ -2594,6 +2870,9 @@
       <c r="B94" t="s">
         <v>6</v>
       </c>
+      <c r="C94">
+        <v>17181</v>
+      </c>
       <c r="D94" t="s">
         <v>8</v>
       </c>
@@ -2617,6 +2896,9 @@
       <c r="B95" t="s">
         <v>6</v>
       </c>
+      <c r="C95">
+        <v>17910</v>
+      </c>
       <c r="D95" t="s">
         <v>8</v>
       </c>
@@ -2640,6 +2922,9 @@
       <c r="B96" t="s">
         <v>6</v>
       </c>
+      <c r="C96">
+        <v>18310</v>
+      </c>
       <c r="D96" t="s">
         <v>8</v>
       </c>
@@ -2663,6 +2948,9 @@
       <c r="B97" t="s">
         <v>6</v>
       </c>
+      <c r="C97">
+        <v>15632</v>
+      </c>
       <c r="D97" t="s">
         <v>8</v>
       </c>
@@ -2686,6 +2974,9 @@
       <c r="B98" t="s">
         <v>6</v>
       </c>
+      <c r="C98">
+        <v>17093</v>
+      </c>
       <c r="D98" t="s">
         <v>8</v>
       </c>
@@ -2709,6 +3000,9 @@
       <c r="B99" t="s">
         <v>6</v>
       </c>
+      <c r="C99">
+        <v>23264</v>
+      </c>
       <c r="D99" t="s">
         <v>8</v>
       </c>
@@ -2732,6 +3026,9 @@
       <c r="B100" t="s">
         <v>6</v>
       </c>
+      <c r="C100">
+        <v>15585</v>
+      </c>
       <c r="D100" t="s">
         <v>8</v>
       </c>
@@ -2755,6 +3052,9 @@
       <c r="B101" t="s">
         <v>6</v>
       </c>
+      <c r="C101">
+        <v>12418</v>
+      </c>
       <c r="D101" t="s">
         <v>8</v>
       </c>
@@ -2778,6 +3078,9 @@
       <c r="B102" t="s">
         <v>9</v>
       </c>
+      <c r="C102">
+        <v>19759</v>
+      </c>
       <c r="D102" t="s">
         <v>8</v>
       </c>
@@ -2801,6 +3104,9 @@
       <c r="B103" t="s">
         <v>9</v>
       </c>
+      <c r="C103">
+        <v>21205</v>
+      </c>
       <c r="D103" t="s">
         <v>8</v>
       </c>
@@ -2824,6 +3130,9 @@
       <c r="B104" t="s">
         <v>9</v>
       </c>
+      <c r="C104">
+        <v>24775</v>
+      </c>
       <c r="D104" t="s">
         <v>8</v>
       </c>
@@ -2847,6 +3156,9 @@
       <c r="B105" t="s">
         <v>9</v>
       </c>
+      <c r="C105">
+        <v>20404</v>
+      </c>
       <c r="D105" t="s">
         <v>8</v>
       </c>
@@ -2870,6 +3182,9 @@
       <c r="B106" t="s">
         <v>9</v>
       </c>
+      <c r="C106">
+        <v>19818</v>
+      </c>
       <c r="D106" t="s">
         <v>8</v>
       </c>
@@ -2893,6 +3208,9 @@
       <c r="B107" t="s">
         <v>9</v>
       </c>
+      <c r="C107">
+        <v>19107</v>
+      </c>
       <c r="D107" t="s">
         <v>8</v>
       </c>
@@ -2916,6 +3234,9 @@
       <c r="B108" t="s">
         <v>9</v>
       </c>
+      <c r="C108">
+        <v>15866</v>
+      </c>
       <c r="D108" t="s">
         <v>8</v>
       </c>
@@ -2939,6 +3260,9 @@
       <c r="B109" t="s">
         <v>9</v>
       </c>
+      <c r="C109">
+        <v>20245</v>
+      </c>
       <c r="D109" t="s">
         <v>8</v>
       </c>
@@ -2962,6 +3286,9 @@
       <c r="B110" t="s">
         <v>9</v>
       </c>
+      <c r="C110">
+        <v>19851</v>
+      </c>
       <c r="D110" t="s">
         <v>8</v>
       </c>
@@ -2985,6 +3312,9 @@
       <c r="B111" t="s">
         <v>9</v>
       </c>
+      <c r="C111">
+        <v>18618</v>
+      </c>
       <c r="D111" t="s">
         <v>8</v>
       </c>
@@ -3008,6 +3338,9 @@
       <c r="B112" t="s">
         <v>9</v>
       </c>
+      <c r="C112">
+        <v>18521</v>
+      </c>
       <c r="D112" t="s">
         <v>8</v>
       </c>
@@ -3031,6 +3364,9 @@
       <c r="B113" t="s">
         <v>9</v>
       </c>
+      <c r="C113">
+        <v>20627</v>
+      </c>
       <c r="D113" t="s">
         <v>8</v>
       </c>
@@ -3054,6 +3390,9 @@
       <c r="B114" t="s">
         <v>9</v>
       </c>
+      <c r="C114">
+        <v>18372</v>
+      </c>
       <c r="D114" t="s">
         <v>8</v>
       </c>
@@ -3077,6 +3416,9 @@
       <c r="B115" t="s">
         <v>9</v>
       </c>
+      <c r="C115">
+        <v>18594</v>
+      </c>
       <c r="D115" t="s">
         <v>8</v>
       </c>
@@ -3100,6 +3442,9 @@
       <c r="B116" t="s">
         <v>9</v>
       </c>
+      <c r="C116">
+        <v>21549</v>
+      </c>
       <c r="D116" t="s">
         <v>8</v>
       </c>
@@ -3123,6 +3468,9 @@
       <c r="B117" t="s">
         <v>9</v>
       </c>
+      <c r="C117">
+        <v>19314</v>
+      </c>
       <c r="D117" t="s">
         <v>8</v>
       </c>
@@ -3146,6 +3494,9 @@
       <c r="B118" t="s">
         <v>9</v>
       </c>
+      <c r="C118">
+        <v>19146</v>
+      </c>
       <c r="D118" t="s">
         <v>8</v>
       </c>
@@ -3169,6 +3520,9 @@
       <c r="B119" t="s">
         <v>9</v>
       </c>
+      <c r="C119">
+        <v>20854</v>
+      </c>
       <c r="D119" t="s">
         <v>8</v>
       </c>
@@ -3192,6 +3546,9 @@
       <c r="B120" t="s">
         <v>9</v>
       </c>
+      <c r="C120">
+        <v>22689</v>
+      </c>
       <c r="D120" t="s">
         <v>8</v>
       </c>
@@ -3215,6 +3572,9 @@
       <c r="B121" t="s">
         <v>9</v>
       </c>
+      <c r="C121">
+        <v>21217</v>
+      </c>
       <c r="D121" t="s">
         <v>8</v>
       </c>
@@ -3238,6 +3598,9 @@
       <c r="B122" t="s">
         <v>9</v>
       </c>
+      <c r="C122">
+        <v>18080</v>
+      </c>
       <c r="D122" t="s">
         <v>8</v>
       </c>
@@ -3261,6 +3624,9 @@
       <c r="B123" t="s">
         <v>9</v>
       </c>
+      <c r="C123">
+        <v>19725</v>
+      </c>
       <c r="D123" t="s">
         <v>8</v>
       </c>
@@ -3284,6 +3650,9 @@
       <c r="B124" t="s">
         <v>9</v>
       </c>
+      <c r="C124">
+        <v>19012</v>
+      </c>
       <c r="D124" t="s">
         <v>8</v>
       </c>
@@ -3307,6 +3676,9 @@
       <c r="B125" t="s">
         <v>9</v>
       </c>
+      <c r="C125">
+        <v>27235</v>
+      </c>
       <c r="D125" t="s">
         <v>8</v>
       </c>
@@ -3330,6 +3702,9 @@
       <c r="B126" t="s">
         <v>9</v>
       </c>
+      <c r="C126">
+        <v>19424</v>
+      </c>
       <c r="D126" t="s">
         <v>8</v>
       </c>
@@ -3353,6 +3728,9 @@
       <c r="B127" t="s">
         <v>9</v>
       </c>
+      <c r="C127">
+        <v>21139</v>
+      </c>
       <c r="D127" t="s">
         <v>8</v>
       </c>
@@ -3376,6 +3754,9 @@
       <c r="B128" t="s">
         <v>9</v>
       </c>
+      <c r="C128">
+        <v>9685</v>
+      </c>
       <c r="D128" t="s">
         <v>8</v>
       </c>
@@ -3399,6 +3780,9 @@
       <c r="B129" t="s">
         <v>9</v>
       </c>
+      <c r="C129">
+        <v>19560</v>
+      </c>
       <c r="D129" t="s">
         <v>8</v>
       </c>
@@ -3422,6 +3806,9 @@
       <c r="B130" t="s">
         <v>9</v>
       </c>
+      <c r="C130">
+        <v>20743</v>
+      </c>
       <c r="D130" t="s">
         <v>8</v>
       </c>
@@ -3445,6 +3832,9 @@
       <c r="B131" t="s">
         <v>9</v>
       </c>
+      <c r="C131">
+        <v>20309</v>
+      </c>
       <c r="D131" t="s">
         <v>8</v>
       </c>
@@ -3468,6 +3858,9 @@
       <c r="B132" t="s">
         <v>9</v>
       </c>
+      <c r="C132">
+        <v>19334</v>
+      </c>
       <c r="D132" t="s">
         <v>8</v>
       </c>
@@ -3491,6 +3884,9 @@
       <c r="B133" t="s">
         <v>9</v>
       </c>
+      <c r="C133">
+        <v>19855</v>
+      </c>
       <c r="D133" t="s">
         <v>8</v>
       </c>
@@ -3514,6 +3910,9 @@
       <c r="B134" t="s">
         <v>9</v>
       </c>
+      <c r="C134">
+        <v>21295</v>
+      </c>
       <c r="D134" t="s">
         <v>8</v>
       </c>
@@ -3537,6 +3936,9 @@
       <c r="B135" t="s">
         <v>9</v>
       </c>
+      <c r="C135">
+        <v>19548</v>
+      </c>
       <c r="D135" t="s">
         <v>8</v>
       </c>
@@ -3560,6 +3962,9 @@
       <c r="B136" t="s">
         <v>9</v>
       </c>
+      <c r="C136">
+        <v>20794</v>
+      </c>
       <c r="D136" t="s">
         <v>8</v>
       </c>
@@ -3583,6 +3988,9 @@
       <c r="B137" t="s">
         <v>9</v>
       </c>
+      <c r="C137">
+        <v>17858</v>
+      </c>
       <c r="D137" t="s">
         <v>8</v>
       </c>
@@ -3606,6 +4014,9 @@
       <c r="B138" t="s">
         <v>9</v>
       </c>
+      <c r="C138">
+        <v>20599</v>
+      </c>
       <c r="D138" t="s">
         <v>8</v>
       </c>
@@ -3629,6 +4040,9 @@
       <c r="B139" t="s">
         <v>9</v>
       </c>
+      <c r="C139">
+        <v>20101</v>
+      </c>
       <c r="D139" t="s">
         <v>8</v>
       </c>
@@ -3652,6 +4066,9 @@
       <c r="B140" t="s">
         <v>9</v>
       </c>
+      <c r="C140">
+        <v>19031</v>
+      </c>
       <c r="D140" t="s">
         <v>8</v>
       </c>
@@ -3675,6 +4092,9 @@
       <c r="B141" t="s">
         <v>9</v>
       </c>
+      <c r="C141">
+        <v>20483</v>
+      </c>
       <c r="D141" t="s">
         <v>8</v>
       </c>
@@ -3698,6 +4118,9 @@
       <c r="B142" t="s">
         <v>9</v>
       </c>
+      <c r="C142">
+        <v>20248</v>
+      </c>
       <c r="D142" t="s">
         <v>8</v>
       </c>
@@ -3721,6 +4144,9 @@
       <c r="B143" t="s">
         <v>9</v>
       </c>
+      <c r="C143">
+        <v>18191</v>
+      </c>
       <c r="D143" t="s">
         <v>8</v>
       </c>
@@ -3744,6 +4170,9 @@
       <c r="B144" t="s">
         <v>9</v>
       </c>
+      <c r="C144">
+        <v>21878</v>
+      </c>
       <c r="D144" t="s">
         <v>8</v>
       </c>
@@ -3767,6 +4196,9 @@
       <c r="B145" t="s">
         <v>9</v>
       </c>
+      <c r="C145">
+        <v>25490</v>
+      </c>
       <c r="D145" t="s">
         <v>8</v>
       </c>
@@ -3790,6 +4222,9 @@
       <c r="B146" t="s">
         <v>9</v>
       </c>
+      <c r="C146">
+        <v>6782</v>
+      </c>
       <c r="D146" t="s">
         <v>8</v>
       </c>
@@ -3813,6 +4248,9 @@
       <c r="B147" t="s">
         <v>9</v>
       </c>
+      <c r="C147">
+        <v>20208</v>
+      </c>
       <c r="D147" t="s">
         <v>8</v>
       </c>
@@ -3836,6 +4274,9 @@
       <c r="B148" t="s">
         <v>9</v>
       </c>
+      <c r="C148">
+        <v>18593</v>
+      </c>
       <c r="D148" t="s">
         <v>8</v>
       </c>
@@ -3859,6 +4300,9 @@
       <c r="B149" t="s">
         <v>9</v>
       </c>
+      <c r="C149">
+        <v>20634</v>
+      </c>
       <c r="D149" t="s">
         <v>8</v>
       </c>
@@ -3882,6 +4326,9 @@
       <c r="B150" t="s">
         <v>9</v>
       </c>
+      <c r="C150">
+        <v>18676</v>
+      </c>
       <c r="D150" t="s">
         <v>8</v>
       </c>
@@ -3905,6 +4352,9 @@
       <c r="B151" t="s">
         <v>9</v>
       </c>
+      <c r="C151">
+        <v>24730</v>
+      </c>
       <c r="D151" t="s">
         <v>8</v>
       </c>
@@ -3928,6 +4378,9 @@
       <c r="B152" t="s">
         <v>9</v>
       </c>
+      <c r="C152">
+        <v>18222</v>
+      </c>
       <c r="D152" t="s">
         <v>8</v>
       </c>
@@ -3951,6 +4404,9 @@
       <c r="B153" t="s">
         <v>9</v>
       </c>
+      <c r="C153">
+        <v>17495</v>
+      </c>
       <c r="D153" t="s">
         <v>8</v>
       </c>
@@ -3974,6 +4430,9 @@
       <c r="B154" t="s">
         <v>9</v>
       </c>
+      <c r="C154">
+        <v>24203</v>
+      </c>
       <c r="D154" t="s">
         <v>8</v>
       </c>
@@ -3997,6 +4456,9 @@
       <c r="B155" t="s">
         <v>9</v>
       </c>
+      <c r="C155">
+        <v>22361</v>
+      </c>
       <c r="D155" t="s">
         <v>8</v>
       </c>
@@ -4020,6 +4482,9 @@
       <c r="B156" t="s">
         <v>9</v>
       </c>
+      <c r="C156">
+        <v>18318</v>
+      </c>
       <c r="D156" t="s">
         <v>8</v>
       </c>
@@ -4043,6 +4508,9 @@
       <c r="B157" t="s">
         <v>9</v>
       </c>
+      <c r="C157">
+        <v>18741</v>
+      </c>
       <c r="D157" t="s">
         <v>8</v>
       </c>
@@ -4066,6 +4534,9 @@
       <c r="B158" t="s">
         <v>9</v>
       </c>
+      <c r="C158">
+        <v>22015</v>
+      </c>
       <c r="D158" t="s">
         <v>8</v>
       </c>
@@ -4089,6 +4560,9 @@
       <c r="B159" t="s">
         <v>9</v>
       </c>
+      <c r="C159">
+        <v>20920</v>
+      </c>
       <c r="D159" t="s">
         <v>8</v>
       </c>
@@ -4112,6 +4586,9 @@
       <c r="B160" t="s">
         <v>9</v>
       </c>
+      <c r="C160">
+        <v>19273</v>
+      </c>
       <c r="D160" t="s">
         <v>8</v>
       </c>
@@ -4135,6 +4612,9 @@
       <c r="B161" t="s">
         <v>9</v>
       </c>
+      <c r="C161">
+        <v>19909</v>
+      </c>
       <c r="D161" t="s">
         <v>8</v>
       </c>
@@ -4158,6 +4638,9 @@
       <c r="B162" t="s">
         <v>9</v>
       </c>
+      <c r="C162">
+        <v>21759</v>
+      </c>
       <c r="D162" t="s">
         <v>8</v>
       </c>
@@ -4181,6 +4664,9 @@
       <c r="B163" t="s">
         <v>9</v>
       </c>
+      <c r="C163">
+        <v>17351</v>
+      </c>
       <c r="D163" t="s">
         <v>8</v>
       </c>
@@ -4204,6 +4690,9 @@
       <c r="B164" t="s">
         <v>9</v>
       </c>
+      <c r="C164">
+        <v>22677</v>
+      </c>
       <c r="D164" t="s">
         <v>8</v>
       </c>
@@ -4227,6 +4716,9 @@
       <c r="B165" t="s">
         <v>9</v>
       </c>
+      <c r="C165">
+        <v>22067</v>
+      </c>
       <c r="D165" t="s">
         <v>8</v>
       </c>
@@ -4250,6 +4742,9 @@
       <c r="B166" t="s">
         <v>9</v>
       </c>
+      <c r="C166">
+        <v>18337</v>
+      </c>
       <c r="D166" t="s">
         <v>8</v>
       </c>
@@ -4273,6 +4768,9 @@
       <c r="B167" t="s">
         <v>9</v>
       </c>
+      <c r="C167">
+        <v>18601</v>
+      </c>
       <c r="D167" t="s">
         <v>8</v>
       </c>
@@ -4296,6 +4794,9 @@
       <c r="B168" t="s">
         <v>9</v>
       </c>
+      <c r="C168">
+        <v>18654</v>
+      </c>
       <c r="D168" t="s">
         <v>8</v>
       </c>
@@ -4319,6 +4820,9 @@
       <c r="B169" t="s">
         <v>9</v>
       </c>
+      <c r="C169">
+        <v>20312</v>
+      </c>
       <c r="D169" t="s">
         <v>8</v>
       </c>
@@ -4342,6 +4846,9 @@
       <c r="B170" t="s">
         <v>9</v>
       </c>
+      <c r="C170">
+        <v>19596</v>
+      </c>
       <c r="D170" t="s">
         <v>8</v>
       </c>
@@ -4365,6 +4872,9 @@
       <c r="B171" t="s">
         <v>9</v>
       </c>
+      <c r="C171">
+        <v>17557</v>
+      </c>
       <c r="D171" t="s">
         <v>8</v>
       </c>
@@ -4388,6 +4898,9 @@
       <c r="B172" t="s">
         <v>9</v>
       </c>
+      <c r="C172">
+        <v>19684</v>
+      </c>
       <c r="D172" t="s">
         <v>8</v>
       </c>
@@ -4411,6 +4924,9 @@
       <c r="B173" t="s">
         <v>9</v>
       </c>
+      <c r="C173">
+        <v>18818</v>
+      </c>
       <c r="D173" t="s">
         <v>8</v>
       </c>
@@ -4434,6 +4950,9 @@
       <c r="B174" t="s">
         <v>9</v>
       </c>
+      <c r="C174">
+        <v>18888</v>
+      </c>
       <c r="D174" t="s">
         <v>8</v>
       </c>
@@ -4457,6 +4976,9 @@
       <c r="B175" t="s">
         <v>9</v>
       </c>
+      <c r="C175">
+        <v>20777</v>
+      </c>
       <c r="D175" t="s">
         <v>8</v>
       </c>
@@ -4480,6 +5002,9 @@
       <c r="B176" t="s">
         <v>9</v>
       </c>
+      <c r="C176">
+        <v>19199</v>
+      </c>
       <c r="D176" t="s">
         <v>8</v>
       </c>
@@ -4503,6 +5028,9 @@
       <c r="B177" t="s">
         <v>9</v>
       </c>
+      <c r="C177">
+        <v>20639</v>
+      </c>
       <c r="D177" t="s">
         <v>8</v>
       </c>
@@ -4526,6 +5054,9 @@
       <c r="B178" t="s">
         <v>9</v>
       </c>
+      <c r="C178">
+        <v>19413</v>
+      </c>
       <c r="D178" t="s">
         <v>8</v>
       </c>
@@ -4549,6 +5080,9 @@
       <c r="B179" t="s">
         <v>9</v>
       </c>
+      <c r="C179">
+        <v>24694</v>
+      </c>
       <c r="D179" t="s">
         <v>8</v>
       </c>
@@ -4572,6 +5106,9 @@
       <c r="B180" t="s">
         <v>9</v>
       </c>
+      <c r="C180">
+        <v>18393</v>
+      </c>
       <c r="D180" t="s">
         <v>8</v>
       </c>
@@ -4595,6 +5132,9 @@
       <c r="B181" t="s">
         <v>9</v>
       </c>
+      <c r="C181">
+        <v>20395</v>
+      </c>
       <c r="D181" t="s">
         <v>8</v>
       </c>
@@ -4618,6 +5158,9 @@
       <c r="B182" t="s">
         <v>9</v>
       </c>
+      <c r="C182">
+        <v>22067</v>
+      </c>
       <c r="D182" t="s">
         <v>8</v>
       </c>
@@ -4641,6 +5184,9 @@
       <c r="B183" t="s">
         <v>9</v>
       </c>
+      <c r="C183">
+        <v>20997</v>
+      </c>
       <c r="D183" t="s">
         <v>8</v>
       </c>
@@ -4664,6 +5210,9 @@
       <c r="B184" t="s">
         <v>9</v>
       </c>
+      <c r="C184">
+        <v>23621</v>
+      </c>
       <c r="D184" t="s">
         <v>8</v>
       </c>
@@ -4687,6 +5236,9 @@
       <c r="B185" t="s">
         <v>9</v>
       </c>
+      <c r="C185">
+        <v>19785</v>
+      </c>
       <c r="D185" t="s">
         <v>8</v>
       </c>
@@ -4710,6 +5262,9 @@
       <c r="B186" t="s">
         <v>9</v>
       </c>
+      <c r="C186">
+        <v>19621</v>
+      </c>
       <c r="D186" t="s">
         <v>8</v>
       </c>
@@ -4733,6 +5288,9 @@
       <c r="B187" t="s">
         <v>9</v>
       </c>
+      <c r="C187">
+        <v>21327</v>
+      </c>
       <c r="D187" t="s">
         <v>8</v>
       </c>
@@ -4756,6 +5314,9 @@
       <c r="B188" t="s">
         <v>9</v>
       </c>
+      <c r="C188">
+        <v>21650</v>
+      </c>
       <c r="D188" t="s">
         <v>8</v>
       </c>
@@ -4779,6 +5340,9 @@
       <c r="B189" t="s">
         <v>9</v>
       </c>
+      <c r="C189">
+        <v>22856</v>
+      </c>
       <c r="D189" t="s">
         <v>8</v>
       </c>
@@ -4802,6 +5366,9 @@
       <c r="B190" t="s">
         <v>9</v>
       </c>
+      <c r="C190">
+        <v>18524</v>
+      </c>
       <c r="D190" t="s">
         <v>8</v>
       </c>
@@ -4825,6 +5392,9 @@
       <c r="B191" t="s">
         <v>9</v>
       </c>
+      <c r="C191">
+        <v>20209</v>
+      </c>
       <c r="D191" t="s">
         <v>8</v>
       </c>
@@ -4848,6 +5418,9 @@
       <c r="B192" t="s">
         <v>9</v>
       </c>
+      <c r="C192">
+        <v>22606</v>
+      </c>
       <c r="D192" t="s">
         <v>8</v>
       </c>
@@ -4871,6 +5444,9 @@
       <c r="B193" t="s">
         <v>9</v>
       </c>
+      <c r="C193">
+        <v>21839</v>
+      </c>
       <c r="D193" t="s">
         <v>8</v>
       </c>
@@ -4894,6 +5470,9 @@
       <c r="B194" t="s">
         <v>9</v>
       </c>
+      <c r="C194">
+        <v>23308</v>
+      </c>
       <c r="D194" t="s">
         <v>8</v>
       </c>
@@ -4917,6 +5496,9 @@
       <c r="B195" t="s">
         <v>9</v>
       </c>
+      <c r="C195">
+        <v>17418</v>
+      </c>
       <c r="D195" t="s">
         <v>8</v>
       </c>
@@ -4940,6 +5522,9 @@
       <c r="B196" t="s">
         <v>9</v>
       </c>
+      <c r="C196">
+        <v>20593</v>
+      </c>
       <c r="D196" t="s">
         <v>8</v>
       </c>
@@ -4963,6 +5548,9 @@
       <c r="B197" t="s">
         <v>9</v>
       </c>
+      <c r="C197">
+        <v>19385</v>
+      </c>
       <c r="D197" t="s">
         <v>8</v>
       </c>
@@ -4986,6 +5574,9 @@
       <c r="B198" t="s">
         <v>9</v>
       </c>
+      <c r="C198">
+        <v>20579</v>
+      </c>
       <c r="D198" t="s">
         <v>8</v>
       </c>
@@ -5009,6 +5600,9 @@
       <c r="B199" t="s">
         <v>9</v>
       </c>
+      <c r="C199">
+        <v>18450</v>
+      </c>
       <c r="D199" t="s">
         <v>8</v>
       </c>
@@ -5032,6 +5626,9 @@
       <c r="B200" t="s">
         <v>9</v>
       </c>
+      <c r="C200">
+        <v>19071</v>
+      </c>
       <c r="D200" t="s">
         <v>8</v>
       </c>
@@ -5054,6 +5651,9 @@
       </c>
       <c r="B201" t="s">
         <v>9</v>
+      </c>
+      <c r="C201">
+        <v>19449</v>
       </c>
       <c r="D201" t="s">
         <v>8</v>

--- a/Time to Fixation Experiments - Changing Chemotaxis Equation/Combined_Time_Fix_Data.xlsx
+++ b/Time to Fixation Experiments - Changing Chemotaxis Equation/Combined_Time_Fix_Data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Moar Documents\GitHub\Bac_Evol_SSA\Time to Fixation Experiments - Changing Chemotaxis Equation\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{237C5703-45D3-4B40-AC7D-C11063AFE222}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C347C917-0D17-4E7C-9951-2316699543E9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1596" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1608" uniqueCount="17">
   <si>
     <t>Condition</t>
   </si>
@@ -434,7 +434,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I795"/>
+  <dimension ref="A1:I801"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="16.140625" bestFit="1" customWidth="1"/>
@@ -16078,6 +16078,9 @@
       <c r="B602" t="s">
         <v>7</v>
       </c>
+      <c r="C602">
+        <v>17623</v>
+      </c>
       <c r="D602" t="s">
         <v>14</v>
       </c>
@@ -16101,6 +16104,9 @@
       <c r="B603" t="s">
         <v>7</v>
       </c>
+      <c r="C603">
+        <v>21652</v>
+      </c>
       <c r="D603" t="s">
         <v>14</v>
       </c>
@@ -16124,6 +16130,9 @@
       <c r="B604" t="s">
         <v>7</v>
       </c>
+      <c r="C604">
+        <v>20515</v>
+      </c>
       <c r="D604" t="s">
         <v>14</v>
       </c>
@@ -16147,6 +16156,9 @@
       <c r="B605" t="s">
         <v>7</v>
       </c>
+      <c r="C605">
+        <v>19787</v>
+      </c>
       <c r="D605" t="s">
         <v>14</v>
       </c>
@@ -16170,6 +16182,9 @@
       <c r="B606" t="s">
         <v>7</v>
       </c>
+      <c r="C606">
+        <v>19868</v>
+      </c>
       <c r="D606" t="s">
         <v>14</v>
       </c>
@@ -16193,6 +16208,9 @@
       <c r="B607" t="s">
         <v>7</v>
       </c>
+      <c r="C607">
+        <v>19822</v>
+      </c>
       <c r="D607" t="s">
         <v>14</v>
       </c>
@@ -16216,6 +16234,9 @@
       <c r="B608" t="s">
         <v>7</v>
       </c>
+      <c r="C608">
+        <v>16763</v>
+      </c>
       <c r="D608" t="s">
         <v>14</v>
       </c>
@@ -16239,6 +16260,9 @@
       <c r="B609" t="s">
         <v>7</v>
       </c>
+      <c r="C609">
+        <v>17699</v>
+      </c>
       <c r="D609" t="s">
         <v>14</v>
       </c>
@@ -16262,6 +16286,9 @@
       <c r="B610" t="s">
         <v>7</v>
       </c>
+      <c r="C610">
+        <v>19191</v>
+      </c>
       <c r="D610" t="s">
         <v>14</v>
       </c>
@@ -16285,6 +16312,9 @@
       <c r="B611" t="s">
         <v>7</v>
       </c>
+      <c r="C611">
+        <v>27387</v>
+      </c>
       <c r="D611" t="s">
         <v>14</v>
       </c>
@@ -16308,6 +16338,9 @@
       <c r="B612" t="s">
         <v>7</v>
       </c>
+      <c r="C612">
+        <v>19778</v>
+      </c>
       <c r="D612" t="s">
         <v>14</v>
       </c>
@@ -16331,6 +16364,9 @@
       <c r="B613" t="s">
         <v>7</v>
       </c>
+      <c r="C613">
+        <v>22791</v>
+      </c>
       <c r="D613" t="s">
         <v>14</v>
       </c>
@@ -16354,6 +16390,9 @@
       <c r="B614" t="s">
         <v>7</v>
       </c>
+      <c r="C614">
+        <v>17237</v>
+      </c>
       <c r="D614" t="s">
         <v>14</v>
       </c>
@@ -16377,6 +16416,9 @@
       <c r="B615" t="s">
         <v>7</v>
       </c>
+      <c r="C615">
+        <v>29302</v>
+      </c>
       <c r="D615" t="s">
         <v>14</v>
       </c>
@@ -16400,6 +16442,9 @@
       <c r="B616" t="s">
         <v>7</v>
       </c>
+      <c r="C616">
+        <v>18526</v>
+      </c>
       <c r="D616" t="s">
         <v>14</v>
       </c>
@@ -16423,6 +16468,9 @@
       <c r="B617" t="s">
         <v>7</v>
       </c>
+      <c r="C617">
+        <v>19676</v>
+      </c>
       <c r="D617" t="s">
         <v>14</v>
       </c>
@@ -16446,6 +16494,9 @@
       <c r="B618" t="s">
         <v>7</v>
       </c>
+      <c r="C618">
+        <v>17917</v>
+      </c>
       <c r="D618" t="s">
         <v>14</v>
       </c>
@@ -16469,6 +16520,9 @@
       <c r="B619" t="s">
         <v>7</v>
       </c>
+      <c r="C619">
+        <v>22714</v>
+      </c>
       <c r="D619" t="s">
         <v>14</v>
       </c>
@@ -16492,6 +16546,9 @@
       <c r="B620" t="s">
         <v>7</v>
       </c>
+      <c r="C620">
+        <v>19125</v>
+      </c>
       <c r="D620" t="s">
         <v>14</v>
       </c>
@@ -16515,6 +16572,9 @@
       <c r="B621" t="s">
         <v>7</v>
       </c>
+      <c r="C621">
+        <v>18403</v>
+      </c>
       <c r="D621" t="s">
         <v>14</v>
       </c>
@@ -16538,6 +16598,9 @@
       <c r="B622" t="s">
         <v>7</v>
       </c>
+      <c r="C622">
+        <v>19929</v>
+      </c>
       <c r="D622" t="s">
         <v>14</v>
       </c>
@@ -16561,6 +16624,9 @@
       <c r="B623" t="s">
         <v>7</v>
       </c>
+      <c r="C623">
+        <v>19198</v>
+      </c>
       <c r="D623" t="s">
         <v>14</v>
       </c>
@@ -16584,6 +16650,9 @@
       <c r="B624" t="s">
         <v>7</v>
       </c>
+      <c r="C624">
+        <v>21127</v>
+      </c>
       <c r="D624" t="s">
         <v>14</v>
       </c>
@@ -16607,6 +16676,9 @@
       <c r="B625" t="s">
         <v>7</v>
       </c>
+      <c r="C625">
+        <v>21274</v>
+      </c>
       <c r="D625" t="s">
         <v>14</v>
       </c>
@@ -16630,6 +16702,9 @@
       <c r="B626" t="s">
         <v>7</v>
       </c>
+      <c r="C626">
+        <v>18723</v>
+      </c>
       <c r="D626" t="s">
         <v>14</v>
       </c>
@@ -16653,6 +16728,9 @@
       <c r="B627" t="s">
         <v>7</v>
       </c>
+      <c r="C627">
+        <v>21532</v>
+      </c>
       <c r="D627" t="s">
         <v>14</v>
       </c>
@@ -16676,6 +16754,9 @@
       <c r="B628" t="s">
         <v>7</v>
       </c>
+      <c r="C628">
+        <v>19670</v>
+      </c>
       <c r="D628" t="s">
         <v>14</v>
       </c>
@@ -16699,6 +16780,9 @@
       <c r="B629" t="s">
         <v>7</v>
       </c>
+      <c r="C629">
+        <v>21113</v>
+      </c>
       <c r="D629" t="s">
         <v>14</v>
       </c>
@@ -16722,6 +16806,9 @@
       <c r="B630" t="s">
         <v>7</v>
       </c>
+      <c r="C630">
+        <v>19465</v>
+      </c>
       <c r="D630" t="s">
         <v>14</v>
       </c>
@@ -16745,6 +16832,9 @@
       <c r="B631" t="s">
         <v>7</v>
       </c>
+      <c r="C631">
+        <v>16728</v>
+      </c>
       <c r="D631" t="s">
         <v>14</v>
       </c>
@@ -16768,6 +16858,9 @@
       <c r="B632" t="s">
         <v>7</v>
       </c>
+      <c r="C632">
+        <v>21089</v>
+      </c>
       <c r="D632" t="s">
         <v>14</v>
       </c>
@@ -16791,6 +16884,9 @@
       <c r="B633" t="s">
         <v>7</v>
       </c>
+      <c r="C633">
+        <v>23554</v>
+      </c>
       <c r="D633" t="s">
         <v>14</v>
       </c>
@@ -16814,6 +16910,9 @@
       <c r="B634" t="s">
         <v>7</v>
       </c>
+      <c r="C634">
+        <v>19923</v>
+      </c>
       <c r="D634" t="s">
         <v>14</v>
       </c>
@@ -16837,6 +16936,9 @@
       <c r="B635" t="s">
         <v>7</v>
       </c>
+      <c r="C635">
+        <v>18413</v>
+      </c>
       <c r="D635" t="s">
         <v>14</v>
       </c>
@@ -16860,6 +16962,9 @@
       <c r="B636" t="s">
         <v>7</v>
       </c>
+      <c r="C636">
+        <v>20004</v>
+      </c>
       <c r="D636" t="s">
         <v>14</v>
       </c>
@@ -16883,6 +16988,9 @@
       <c r="B637" t="s">
         <v>7</v>
       </c>
+      <c r="C637">
+        <v>21440</v>
+      </c>
       <c r="D637" t="s">
         <v>14</v>
       </c>
@@ -16906,6 +17014,9 @@
       <c r="B638" t="s">
         <v>7</v>
       </c>
+      <c r="C638">
+        <v>20410</v>
+      </c>
       <c r="D638" t="s">
         <v>14</v>
       </c>
@@ -16929,6 +17040,9 @@
       <c r="B639" t="s">
         <v>7</v>
       </c>
+      <c r="C639">
+        <v>18257</v>
+      </c>
       <c r="D639" t="s">
         <v>14</v>
       </c>
@@ -16952,6 +17066,9 @@
       <c r="B640" t="s">
         <v>7</v>
       </c>
+      <c r="C640">
+        <v>18387</v>
+      </c>
       <c r="D640" t="s">
         <v>14</v>
       </c>
@@ -16975,6 +17092,9 @@
       <c r="B641" t="s">
         <v>7</v>
       </c>
+      <c r="C641">
+        <v>17769</v>
+      </c>
       <c r="D641" t="s">
         <v>14</v>
       </c>
@@ -16998,6 +17118,9 @@
       <c r="B642" t="s">
         <v>7</v>
       </c>
+      <c r="C642">
+        <v>18215</v>
+      </c>
       <c r="D642" t="s">
         <v>14</v>
       </c>
@@ -17021,6 +17144,9 @@
       <c r="B643" t="s">
         <v>7</v>
       </c>
+      <c r="C643">
+        <v>18278</v>
+      </c>
       <c r="D643" t="s">
         <v>14</v>
       </c>
@@ -17044,6 +17170,9 @@
       <c r="B644" t="s">
         <v>7</v>
       </c>
+      <c r="C644">
+        <v>15891</v>
+      </c>
       <c r="D644" t="s">
         <v>14</v>
       </c>
@@ -17067,6 +17196,9 @@
       <c r="B645" t="s">
         <v>7</v>
       </c>
+      <c r="C645">
+        <v>18170</v>
+      </c>
       <c r="D645" t="s">
         <v>14</v>
       </c>
@@ -17090,6 +17222,9 @@
       <c r="B646" t="s">
         <v>7</v>
       </c>
+      <c r="C646">
+        <v>16296</v>
+      </c>
       <c r="D646" t="s">
         <v>14</v>
       </c>
@@ -17113,6 +17248,9 @@
       <c r="B647" t="s">
         <v>7</v>
       </c>
+      <c r="C647">
+        <v>18997</v>
+      </c>
       <c r="D647" t="s">
         <v>14</v>
       </c>
@@ -17136,6 +17274,9 @@
       <c r="B648" t="s">
         <v>7</v>
       </c>
+      <c r="C648">
+        <v>18869</v>
+      </c>
       <c r="D648" t="s">
         <v>14</v>
       </c>
@@ -17159,6 +17300,9 @@
       <c r="B649" t="s">
         <v>7</v>
       </c>
+      <c r="C649">
+        <v>22535</v>
+      </c>
       <c r="D649" t="s">
         <v>14</v>
       </c>
@@ -17182,6 +17326,9 @@
       <c r="B650" t="s">
         <v>7</v>
       </c>
+      <c r="C650">
+        <v>21755</v>
+      </c>
       <c r="D650" t="s">
         <v>14</v>
       </c>
@@ -17205,6 +17352,9 @@
       <c r="B651" t="s">
         <v>7</v>
       </c>
+      <c r="C651">
+        <v>21313</v>
+      </c>
       <c r="D651" t="s">
         <v>14</v>
       </c>
@@ -17228,6 +17378,9 @@
       <c r="B652" t="s">
         <v>7</v>
       </c>
+      <c r="C652">
+        <v>17382</v>
+      </c>
       <c r="D652" t="s">
         <v>14</v>
       </c>
@@ -17251,6 +17404,9 @@
       <c r="B653" t="s">
         <v>7</v>
       </c>
+      <c r="C653">
+        <v>14158</v>
+      </c>
       <c r="D653" t="s">
         <v>14</v>
       </c>
@@ -17274,6 +17430,9 @@
       <c r="B654" t="s">
         <v>7</v>
       </c>
+      <c r="C654">
+        <v>20453</v>
+      </c>
       <c r="D654" t="s">
         <v>14</v>
       </c>
@@ -17297,6 +17456,9 @@
       <c r="B655" t="s">
         <v>7</v>
       </c>
+      <c r="C655">
+        <v>22570</v>
+      </c>
       <c r="D655" t="s">
         <v>14</v>
       </c>
@@ -17320,6 +17482,9 @@
       <c r="B656" t="s">
         <v>7</v>
       </c>
+      <c r="C656">
+        <v>19834</v>
+      </c>
       <c r="D656" t="s">
         <v>14</v>
       </c>
@@ -17343,6 +17508,9 @@
       <c r="B657" t="s">
         <v>7</v>
       </c>
+      <c r="C657">
+        <v>18073</v>
+      </c>
       <c r="D657" t="s">
         <v>14</v>
       </c>
@@ -17366,6 +17534,9 @@
       <c r="B658" t="s">
         <v>7</v>
       </c>
+      <c r="C658">
+        <v>18467</v>
+      </c>
       <c r="D658" t="s">
         <v>14</v>
       </c>
@@ -17389,6 +17560,9 @@
       <c r="B659" t="s">
         <v>7</v>
       </c>
+      <c r="C659">
+        <v>21549</v>
+      </c>
       <c r="D659" t="s">
         <v>14</v>
       </c>
@@ -17412,6 +17586,9 @@
       <c r="B660" t="s">
         <v>7</v>
       </c>
+      <c r="C660">
+        <v>18859</v>
+      </c>
       <c r="D660" t="s">
         <v>14</v>
       </c>
@@ -17435,6 +17612,9 @@
       <c r="B661" t="s">
         <v>7</v>
       </c>
+      <c r="C661">
+        <v>20866</v>
+      </c>
       <c r="D661" t="s">
         <v>14</v>
       </c>
@@ -17458,6 +17638,9 @@
       <c r="B662" t="s">
         <v>7</v>
       </c>
+      <c r="C662">
+        <v>15488</v>
+      </c>
       <c r="D662" t="s">
         <v>14</v>
       </c>
@@ -17481,6 +17664,9 @@
       <c r="B663" t="s">
         <v>7</v>
       </c>
+      <c r="C663">
+        <v>18316</v>
+      </c>
       <c r="D663" t="s">
         <v>14</v>
       </c>
@@ -17504,6 +17690,9 @@
       <c r="B664" t="s">
         <v>7</v>
       </c>
+      <c r="C664">
+        <v>16757</v>
+      </c>
       <c r="D664" t="s">
         <v>14</v>
       </c>
@@ -17527,6 +17716,9 @@
       <c r="B665" t="s">
         <v>7</v>
       </c>
+      <c r="C665">
+        <v>19529</v>
+      </c>
       <c r="D665" t="s">
         <v>14</v>
       </c>
@@ -17550,6 +17742,9 @@
       <c r="B666" t="s">
         <v>7</v>
       </c>
+      <c r="C666">
+        <v>17115</v>
+      </c>
       <c r="D666" t="s">
         <v>14</v>
       </c>
@@ -17573,6 +17768,9 @@
       <c r="B667" t="s">
         <v>7</v>
       </c>
+      <c r="C667">
+        <v>19810</v>
+      </c>
       <c r="D667" t="s">
         <v>14</v>
       </c>
@@ -17596,6 +17794,9 @@
       <c r="B668" t="s">
         <v>7</v>
       </c>
+      <c r="C668">
+        <v>19675</v>
+      </c>
       <c r="D668" t="s">
         <v>14</v>
       </c>
@@ -17619,6 +17820,9 @@
       <c r="B669" t="s">
         <v>7</v>
       </c>
+      <c r="C669">
+        <v>18232</v>
+      </c>
       <c r="D669" t="s">
         <v>14</v>
       </c>
@@ -17642,6 +17846,9 @@
       <c r="B670" t="s">
         <v>7</v>
       </c>
+      <c r="C670">
+        <v>22855</v>
+      </c>
       <c r="D670" t="s">
         <v>14</v>
       </c>
@@ -17665,6 +17872,9 @@
       <c r="B671" t="s">
         <v>7</v>
       </c>
+      <c r="C671">
+        <v>19714</v>
+      </c>
       <c r="D671" t="s">
         <v>14</v>
       </c>
@@ -17688,6 +17898,9 @@
       <c r="B672" t="s">
         <v>7</v>
       </c>
+      <c r="C672">
+        <v>18637</v>
+      </c>
       <c r="D672" t="s">
         <v>14</v>
       </c>
@@ -17711,6 +17924,9 @@
       <c r="B673" t="s">
         <v>7</v>
       </c>
+      <c r="C673">
+        <v>21934</v>
+      </c>
       <c r="D673" t="s">
         <v>14</v>
       </c>
@@ -17734,6 +17950,9 @@
       <c r="B674" t="s">
         <v>7</v>
       </c>
+      <c r="C674">
+        <v>17978</v>
+      </c>
       <c r="D674" t="s">
         <v>14</v>
       </c>
@@ -17757,6 +17976,9 @@
       <c r="B675" t="s">
         <v>7</v>
       </c>
+      <c r="C675">
+        <v>18861</v>
+      </c>
       <c r="D675" t="s">
         <v>14</v>
       </c>
@@ -17780,6 +18002,9 @@
       <c r="B676" t="s">
         <v>7</v>
       </c>
+      <c r="C676">
+        <v>21769</v>
+      </c>
       <c r="D676" t="s">
         <v>14</v>
       </c>
@@ -17803,6 +18028,9 @@
       <c r="B677" t="s">
         <v>7</v>
       </c>
+      <c r="C677">
+        <v>20414</v>
+      </c>
       <c r="D677" t="s">
         <v>14</v>
       </c>
@@ -17826,6 +18054,9 @@
       <c r="B678" t="s">
         <v>7</v>
       </c>
+      <c r="C678">
+        <v>15837</v>
+      </c>
       <c r="D678" t="s">
         <v>14</v>
       </c>
@@ -17849,6 +18080,9 @@
       <c r="B679" t="s">
         <v>7</v>
       </c>
+      <c r="C679">
+        <v>21813</v>
+      </c>
       <c r="D679" t="s">
         <v>14</v>
       </c>
@@ -17872,6 +18106,9 @@
       <c r="B680" t="s">
         <v>7</v>
       </c>
+      <c r="C680">
+        <v>17380</v>
+      </c>
       <c r="D680" t="s">
         <v>14</v>
       </c>
@@ -17895,6 +18132,9 @@
       <c r="B681" t="s">
         <v>7</v>
       </c>
+      <c r="C681">
+        <v>20122</v>
+      </c>
       <c r="D681" t="s">
         <v>14</v>
       </c>
@@ -17918,6 +18158,9 @@
       <c r="B682" t="s">
         <v>7</v>
       </c>
+      <c r="C682">
+        <v>19410</v>
+      </c>
       <c r="D682" t="s">
         <v>14</v>
       </c>
@@ -17941,6 +18184,9 @@
       <c r="B683" t="s">
         <v>7</v>
       </c>
+      <c r="C683">
+        <v>22338</v>
+      </c>
       <c r="D683" t="s">
         <v>14</v>
       </c>
@@ -17964,6 +18210,9 @@
       <c r="B684" t="s">
         <v>7</v>
       </c>
+      <c r="C684">
+        <v>18991</v>
+      </c>
       <c r="D684" t="s">
         <v>14</v>
       </c>
@@ -17987,6 +18236,9 @@
       <c r="B685" t="s">
         <v>7</v>
       </c>
+      <c r="C685">
+        <v>17290</v>
+      </c>
       <c r="D685" t="s">
         <v>14</v>
       </c>
@@ -18010,6 +18262,9 @@
       <c r="B686" t="s">
         <v>7</v>
       </c>
+      <c r="C686">
+        <v>20010</v>
+      </c>
       <c r="D686" t="s">
         <v>14</v>
       </c>
@@ -18033,6 +18288,9 @@
       <c r="B687" t="s">
         <v>7</v>
       </c>
+      <c r="C687">
+        <v>21678</v>
+      </c>
       <c r="D687" t="s">
         <v>14</v>
       </c>
@@ -18056,6 +18314,9 @@
       <c r="B688" t="s">
         <v>7</v>
       </c>
+      <c r="C688">
+        <v>19946</v>
+      </c>
       <c r="D688" t="s">
         <v>14</v>
       </c>
@@ -18079,6 +18340,9 @@
       <c r="B689" t="s">
         <v>7</v>
       </c>
+      <c r="C689">
+        <v>17375</v>
+      </c>
       <c r="D689" t="s">
         <v>14</v>
       </c>
@@ -18102,6 +18366,9 @@
       <c r="B690" t="s">
         <v>7</v>
       </c>
+      <c r="C690">
+        <v>20391</v>
+      </c>
       <c r="D690" t="s">
         <v>14</v>
       </c>
@@ -18125,6 +18392,9 @@
       <c r="B691" t="s">
         <v>7</v>
       </c>
+      <c r="C691">
+        <v>23005</v>
+      </c>
       <c r="D691" t="s">
         <v>14</v>
       </c>
@@ -18148,6 +18418,9 @@
       <c r="B692" t="s">
         <v>7</v>
       </c>
+      <c r="C692">
+        <v>17818</v>
+      </c>
       <c r="D692" t="s">
         <v>14</v>
       </c>
@@ -18171,6 +18444,9 @@
       <c r="B693" t="s">
         <v>7</v>
       </c>
+      <c r="C693">
+        <v>18917</v>
+      </c>
       <c r="D693" t="s">
         <v>14</v>
       </c>
@@ -18194,6 +18470,9 @@
       <c r="B694" t="s">
         <v>7</v>
       </c>
+      <c r="C694">
+        <v>19667</v>
+      </c>
       <c r="D694" t="s">
         <v>14</v>
       </c>
@@ -18217,6 +18496,9 @@
       <c r="B695" t="s">
         <v>7</v>
       </c>
+      <c r="C695">
+        <v>18383</v>
+      </c>
       <c r="D695" t="s">
         <v>14</v>
       </c>
@@ -18238,7 +18520,10 @@
         <v>694</v>
       </c>
       <c r="B696" t="s">
-        <v>15</v>
+        <v>7</v>
+      </c>
+      <c r="C696">
+        <v>19588</v>
       </c>
       <c r="D696" t="s">
         <v>14</v>
@@ -18253,7 +18538,7 @@
         <v>1</v>
       </c>
       <c r="I696" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="697" spans="1:9" x14ac:dyDescent="0.25">
@@ -18261,7 +18546,10 @@
         <v>695</v>
       </c>
       <c r="B697" t="s">
-        <v>15</v>
+        <v>7</v>
+      </c>
+      <c r="C697">
+        <v>18280</v>
       </c>
       <c r="D697" t="s">
         <v>14</v>
@@ -18276,7 +18564,7 @@
         <v>1</v>
       </c>
       <c r="I697" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="698" spans="1:9" x14ac:dyDescent="0.25">
@@ -18284,7 +18572,10 @@
         <v>696</v>
       </c>
       <c r="B698" t="s">
-        <v>15</v>
+        <v>7</v>
+      </c>
+      <c r="C698">
+        <v>25153</v>
       </c>
       <c r="D698" t="s">
         <v>14</v>
@@ -18299,7 +18590,7 @@
         <v>1</v>
       </c>
       <c r="I698" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="699" spans="1:9" x14ac:dyDescent="0.25">
@@ -18307,7 +18598,10 @@
         <v>697</v>
       </c>
       <c r="B699" t="s">
-        <v>15</v>
+        <v>7</v>
+      </c>
+      <c r="C699">
+        <v>20100</v>
       </c>
       <c r="D699" t="s">
         <v>14</v>
@@ -18322,7 +18616,7 @@
         <v>1</v>
       </c>
       <c r="I699" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="700" spans="1:9" x14ac:dyDescent="0.25">
@@ -18330,7 +18624,10 @@
         <v>698</v>
       </c>
       <c r="B700" t="s">
-        <v>15</v>
+        <v>7</v>
+      </c>
+      <c r="C700">
+        <v>16033</v>
       </c>
       <c r="D700" t="s">
         <v>14</v>
@@ -18345,7 +18642,7 @@
         <v>1</v>
       </c>
       <c r="I700" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="701" spans="1:9" x14ac:dyDescent="0.25">
@@ -18353,7 +18650,10 @@
         <v>699</v>
       </c>
       <c r="B701" t="s">
-        <v>15</v>
+        <v>7</v>
+      </c>
+      <c r="C701">
+        <v>19924</v>
       </c>
       <c r="D701" t="s">
         <v>14</v>
@@ -18368,7 +18668,7 @@
         <v>1</v>
       </c>
       <c r="I701" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="702" spans="1:9" x14ac:dyDescent="0.25">
@@ -18378,6 +18678,9 @@
       <c r="B702" t="s">
         <v>15</v>
       </c>
+      <c r="C702">
+        <v>32277</v>
+      </c>
       <c r="D702" t="s">
         <v>14</v>
       </c>
@@ -18401,6 +18704,9 @@
       <c r="B703" t="s">
         <v>15</v>
       </c>
+      <c r="C703">
+        <v>59194</v>
+      </c>
       <c r="D703" t="s">
         <v>14</v>
       </c>
@@ -18424,6 +18730,9 @@
       <c r="B704" t="s">
         <v>15</v>
       </c>
+      <c r="C704">
+        <v>46634</v>
+      </c>
       <c r="D704" t="s">
         <v>14</v>
       </c>
@@ -18447,6 +18756,9 @@
       <c r="B705" t="s">
         <v>15</v>
       </c>
+      <c r="C705">
+        <v>73295</v>
+      </c>
       <c r="D705" t="s">
         <v>14</v>
       </c>
@@ -18470,6 +18782,9 @@
       <c r="B706" t="s">
         <v>15</v>
       </c>
+      <c r="C706">
+        <v>26560</v>
+      </c>
       <c r="D706" t="s">
         <v>14</v>
       </c>
@@ -18493,6 +18808,9 @@
       <c r="B707" t="s">
         <v>15</v>
       </c>
+      <c r="C707">
+        <v>24715</v>
+      </c>
       <c r="D707" t="s">
         <v>14</v>
       </c>
@@ -18516,6 +18834,9 @@
       <c r="B708" t="s">
         <v>15</v>
       </c>
+      <c r="C708">
+        <v>56414</v>
+      </c>
       <c r="D708" t="s">
         <v>14</v>
       </c>
@@ -18539,6 +18860,9 @@
       <c r="B709" t="s">
         <v>15</v>
       </c>
+      <c r="C709">
+        <v>72929</v>
+      </c>
       <c r="D709" t="s">
         <v>14</v>
       </c>
@@ -18562,6 +18886,9 @@
       <c r="B710" t="s">
         <v>15</v>
       </c>
+      <c r="C710">
+        <v>25697</v>
+      </c>
       <c r="D710" t="s">
         <v>14</v>
       </c>
@@ -18585,6 +18912,9 @@
       <c r="B711" t="s">
         <v>15</v>
       </c>
+      <c r="C711">
+        <v>86400</v>
+      </c>
       <c r="D711" t="s">
         <v>14</v>
       </c>
@@ -18608,6 +18938,9 @@
       <c r="B712" t="s">
         <v>15</v>
       </c>
+      <c r="C712">
+        <v>82886</v>
+      </c>
       <c r="D712" t="s">
         <v>14</v>
       </c>
@@ -18631,6 +18964,9 @@
       <c r="B713" t="s">
         <v>15</v>
       </c>
+      <c r="C713">
+        <v>49086</v>
+      </c>
       <c r="D713" t="s">
         <v>14</v>
       </c>
@@ -18654,6 +18990,9 @@
       <c r="B714" t="s">
         <v>15</v>
       </c>
+      <c r="C714">
+        <v>32180</v>
+      </c>
       <c r="D714" t="s">
         <v>14</v>
       </c>
@@ -18677,6 +19016,9 @@
       <c r="B715" t="s">
         <v>15</v>
       </c>
+      <c r="C715">
+        <v>62021</v>
+      </c>
       <c r="D715" t="s">
         <v>14</v>
       </c>
@@ -18700,6 +19042,9 @@
       <c r="B716" t="s">
         <v>15</v>
       </c>
+      <c r="C716">
+        <v>20933</v>
+      </c>
       <c r="D716" t="s">
         <v>14</v>
       </c>
@@ -18723,6 +19068,9 @@
       <c r="B717" t="s">
         <v>15</v>
       </c>
+      <c r="C717">
+        <v>43428</v>
+      </c>
       <c r="D717" t="s">
         <v>14</v>
       </c>
@@ -18746,6 +19094,9 @@
       <c r="B718" t="s">
         <v>15</v>
       </c>
+      <c r="C718">
+        <v>68500</v>
+      </c>
       <c r="D718" t="s">
         <v>14</v>
       </c>
@@ -18769,6 +19120,9 @@
       <c r="B719" t="s">
         <v>15</v>
       </c>
+      <c r="C719">
+        <v>18811</v>
+      </c>
       <c r="D719" t="s">
         <v>14</v>
       </c>
@@ -18792,6 +19146,9 @@
       <c r="B720" t="s">
         <v>15</v>
       </c>
+      <c r="C720">
+        <v>21682</v>
+      </c>
       <c r="D720" t="s">
         <v>14</v>
       </c>
@@ -18815,6 +19172,9 @@
       <c r="B721" t="s">
         <v>15</v>
       </c>
+      <c r="C721">
+        <v>21703</v>
+      </c>
       <c r="D721" t="s">
         <v>14</v>
       </c>
@@ -18838,6 +19198,9 @@
       <c r="B722" t="s">
         <v>15</v>
       </c>
+      <c r="C722">
+        <v>30874</v>
+      </c>
       <c r="D722" t="s">
         <v>14</v>
       </c>
@@ -18861,6 +19224,9 @@
       <c r="B723" t="s">
         <v>15</v>
       </c>
+      <c r="C723">
+        <v>56130</v>
+      </c>
       <c r="D723" t="s">
         <v>14</v>
       </c>
@@ -18884,6 +19250,9 @@
       <c r="B724" t="s">
         <v>15</v>
       </c>
+      <c r="C724">
+        <v>40566</v>
+      </c>
       <c r="D724" t="s">
         <v>14</v>
       </c>
@@ -18907,6 +19276,9 @@
       <c r="B725" t="s">
         <v>15</v>
       </c>
+      <c r="C725">
+        <v>86400</v>
+      </c>
       <c r="D725" t="s">
         <v>14</v>
       </c>
@@ -18930,6 +19302,9 @@
       <c r="B726" t="s">
         <v>15</v>
       </c>
+      <c r="C726">
+        <v>31588</v>
+      </c>
       <c r="D726" t="s">
         <v>14</v>
       </c>
@@ -18953,6 +19328,9 @@
       <c r="B727" t="s">
         <v>15</v>
       </c>
+      <c r="C727">
+        <v>73878</v>
+      </c>
       <c r="D727" t="s">
         <v>14</v>
       </c>
@@ -18976,6 +19354,9 @@
       <c r="B728" t="s">
         <v>15</v>
       </c>
+      <c r="C728">
+        <v>30991</v>
+      </c>
       <c r="D728" t="s">
         <v>14</v>
       </c>
@@ -18999,6 +19380,9 @@
       <c r="B729" t="s">
         <v>15</v>
       </c>
+      <c r="C729">
+        <v>86400</v>
+      </c>
       <c r="D729" t="s">
         <v>14</v>
       </c>
@@ -19022,6 +19406,9 @@
       <c r="B730" t="s">
         <v>15</v>
       </c>
+      <c r="C730">
+        <v>52802</v>
+      </c>
       <c r="D730" t="s">
         <v>14</v>
       </c>
@@ -19045,6 +19432,9 @@
       <c r="B731" t="s">
         <v>15</v>
       </c>
+      <c r="C731">
+        <v>56560</v>
+      </c>
       <c r="D731" t="s">
         <v>14</v>
       </c>
@@ -19068,6 +19458,9 @@
       <c r="B732" t="s">
         <v>15</v>
       </c>
+      <c r="C732">
+        <v>25229</v>
+      </c>
       <c r="D732" t="s">
         <v>14</v>
       </c>
@@ -19091,6 +19484,9 @@
       <c r="B733" t="s">
         <v>15</v>
       </c>
+      <c r="C733">
+        <v>47442</v>
+      </c>
       <c r="D733" t="s">
         <v>14</v>
       </c>
@@ -19114,6 +19510,9 @@
       <c r="B734" t="s">
         <v>15</v>
       </c>
+      <c r="C734">
+        <v>86400</v>
+      </c>
       <c r="D734" t="s">
         <v>14</v>
       </c>
@@ -19137,6 +19536,9 @@
       <c r="B735" t="s">
         <v>15</v>
       </c>
+      <c r="C735">
+        <v>32426</v>
+      </c>
       <c r="D735" t="s">
         <v>14</v>
       </c>
@@ -19160,6 +19562,9 @@
       <c r="B736" t="s">
         <v>15</v>
       </c>
+      <c r="C736">
+        <v>34126</v>
+      </c>
       <c r="D736" t="s">
         <v>14</v>
       </c>
@@ -19183,6 +19588,9 @@
       <c r="B737" t="s">
         <v>15</v>
       </c>
+      <c r="C737">
+        <v>71863</v>
+      </c>
       <c r="D737" t="s">
         <v>14</v>
       </c>
@@ -19206,6 +19614,9 @@
       <c r="B738" t="s">
         <v>15</v>
       </c>
+      <c r="C738">
+        <v>86400</v>
+      </c>
       <c r="D738" t="s">
         <v>14</v>
       </c>
@@ -19229,6 +19640,9 @@
       <c r="B739" t="s">
         <v>15</v>
       </c>
+      <c r="C739">
+        <v>80639</v>
+      </c>
       <c r="D739" t="s">
         <v>14</v>
       </c>
@@ -19252,6 +19666,9 @@
       <c r="B740" t="s">
         <v>15</v>
       </c>
+      <c r="C740">
+        <v>23770</v>
+      </c>
       <c r="D740" t="s">
         <v>14</v>
       </c>
@@ -19275,6 +19692,9 @@
       <c r="B741" t="s">
         <v>15</v>
       </c>
+      <c r="C741">
+        <v>36796</v>
+      </c>
       <c r="D741" t="s">
         <v>14</v>
       </c>
@@ -19298,6 +19718,9 @@
       <c r="B742" t="s">
         <v>15</v>
       </c>
+      <c r="C742">
+        <v>86400</v>
+      </c>
       <c r="D742" t="s">
         <v>14</v>
       </c>
@@ -19321,6 +19744,9 @@
       <c r="B743" t="s">
         <v>15</v>
       </c>
+      <c r="C743">
+        <v>42456</v>
+      </c>
       <c r="D743" t="s">
         <v>14</v>
       </c>
@@ -19344,6 +19770,9 @@
       <c r="B744" t="s">
         <v>15</v>
       </c>
+      <c r="C744">
+        <v>46865</v>
+      </c>
       <c r="D744" t="s">
         <v>14</v>
       </c>
@@ -19367,6 +19796,9 @@
       <c r="B745" t="s">
         <v>15</v>
       </c>
+      <c r="C745">
+        <v>39012</v>
+      </c>
       <c r="D745" t="s">
         <v>14</v>
       </c>
@@ -19390,6 +19822,9 @@
       <c r="B746" t="s">
         <v>15</v>
       </c>
+      <c r="C746">
+        <v>57032</v>
+      </c>
       <c r="D746" t="s">
         <v>14</v>
       </c>
@@ -19413,6 +19848,9 @@
       <c r="B747" t="s">
         <v>15</v>
       </c>
+      <c r="C747">
+        <v>27628</v>
+      </c>
       <c r="D747" t="s">
         <v>14</v>
       </c>
@@ -19436,6 +19874,9 @@
       <c r="B748" t="s">
         <v>15</v>
       </c>
+      <c r="C748">
+        <v>24297</v>
+      </c>
       <c r="D748" t="s">
         <v>14</v>
       </c>
@@ -19459,6 +19900,9 @@
       <c r="B749" t="s">
         <v>15</v>
       </c>
+      <c r="C749">
+        <v>60003</v>
+      </c>
       <c r="D749" t="s">
         <v>14</v>
       </c>
@@ -19482,6 +19926,9 @@
       <c r="B750" t="s">
         <v>15</v>
       </c>
+      <c r="C750">
+        <v>46577</v>
+      </c>
       <c r="D750" t="s">
         <v>14</v>
       </c>
@@ -19505,6 +19952,9 @@
       <c r="B751" t="s">
         <v>15</v>
       </c>
+      <c r="C751">
+        <v>86400</v>
+      </c>
       <c r="D751" t="s">
         <v>14</v>
       </c>
@@ -19528,6 +19978,9 @@
       <c r="B752" t="s">
         <v>15</v>
       </c>
+      <c r="C752">
+        <v>25892</v>
+      </c>
       <c r="D752" t="s">
         <v>14</v>
       </c>
@@ -19551,6 +20004,9 @@
       <c r="B753" t="s">
         <v>15</v>
       </c>
+      <c r="C753">
+        <v>31129</v>
+      </c>
       <c r="D753" t="s">
         <v>14</v>
       </c>
@@ -19574,6 +20030,9 @@
       <c r="B754" t="s">
         <v>15</v>
       </c>
+      <c r="C754">
+        <v>20795</v>
+      </c>
       <c r="D754" t="s">
         <v>14</v>
       </c>
@@ -19597,6 +20056,9 @@
       <c r="B755" t="s">
         <v>15</v>
       </c>
+      <c r="C755">
+        <v>52130</v>
+      </c>
       <c r="D755" t="s">
         <v>14</v>
       </c>
@@ -19620,6 +20082,9 @@
       <c r="B756" t="s">
         <v>15</v>
       </c>
+      <c r="C756">
+        <v>30922</v>
+      </c>
       <c r="D756" t="s">
         <v>14</v>
       </c>
@@ -19643,6 +20108,9 @@
       <c r="B757" t="s">
         <v>15</v>
       </c>
+      <c r="C757">
+        <v>19406</v>
+      </c>
       <c r="D757" t="s">
         <v>14</v>
       </c>
@@ -19666,6 +20134,9 @@
       <c r="B758" t="s">
         <v>15</v>
       </c>
+      <c r="C758">
+        <v>50145</v>
+      </c>
       <c r="D758" t="s">
         <v>14</v>
       </c>
@@ -19689,6 +20160,9 @@
       <c r="B759" t="s">
         <v>15</v>
       </c>
+      <c r="C759">
+        <v>32009</v>
+      </c>
       <c r="D759" t="s">
         <v>14</v>
       </c>
@@ -19712,6 +20186,9 @@
       <c r="B760" t="s">
         <v>15</v>
       </c>
+      <c r="C760">
+        <v>86400</v>
+      </c>
       <c r="D760" t="s">
         <v>14</v>
       </c>
@@ -19735,6 +20212,9 @@
       <c r="B761" t="s">
         <v>15</v>
       </c>
+      <c r="C761">
+        <v>16011</v>
+      </c>
       <c r="D761" t="s">
         <v>14</v>
       </c>
@@ -19758,6 +20238,9 @@
       <c r="B762" t="s">
         <v>15</v>
       </c>
+      <c r="C762">
+        <v>38381</v>
+      </c>
       <c r="D762" t="s">
         <v>14</v>
       </c>
@@ -19781,6 +20264,9 @@
       <c r="B763" t="s">
         <v>15</v>
       </c>
+      <c r="C763">
+        <v>19573</v>
+      </c>
       <c r="D763" t="s">
         <v>14</v>
       </c>
@@ -19804,6 +20290,9 @@
       <c r="B764" t="s">
         <v>15</v>
       </c>
+      <c r="C764">
+        <v>60334</v>
+      </c>
       <c r="D764" t="s">
         <v>14</v>
       </c>
@@ -19827,6 +20316,9 @@
       <c r="B765" t="s">
         <v>15</v>
       </c>
+      <c r="C765">
+        <v>21026</v>
+      </c>
       <c r="D765" t="s">
         <v>14</v>
       </c>
@@ -19850,6 +20342,9 @@
       <c r="B766" t="s">
         <v>15</v>
       </c>
+      <c r="C766">
+        <v>63215</v>
+      </c>
       <c r="D766" t="s">
         <v>14</v>
       </c>
@@ -19873,6 +20368,9 @@
       <c r="B767" t="s">
         <v>15</v>
       </c>
+      <c r="C767">
+        <v>61757</v>
+      </c>
       <c r="D767" t="s">
         <v>14</v>
       </c>
@@ -19896,6 +20394,9 @@
       <c r="B768" t="s">
         <v>15</v>
       </c>
+      <c r="C768">
+        <v>31685</v>
+      </c>
       <c r="D768" t="s">
         <v>14</v>
       </c>
@@ -19919,6 +20420,9 @@
       <c r="B769" t="s">
         <v>15</v>
       </c>
+      <c r="C769">
+        <v>86400</v>
+      </c>
       <c r="D769" t="s">
         <v>14</v>
       </c>
@@ -19942,6 +20446,9 @@
       <c r="B770" t="s">
         <v>15</v>
       </c>
+      <c r="C770">
+        <v>53183</v>
+      </c>
       <c r="D770" t="s">
         <v>14</v>
       </c>
@@ -19965,6 +20472,9 @@
       <c r="B771" t="s">
         <v>15</v>
       </c>
+      <c r="C771">
+        <v>22151</v>
+      </c>
       <c r="D771" t="s">
         <v>14</v>
       </c>
@@ -19988,6 +20498,9 @@
       <c r="B772" t="s">
         <v>15</v>
       </c>
+      <c r="C772">
+        <v>52395</v>
+      </c>
       <c r="D772" t="s">
         <v>14</v>
       </c>
@@ -20011,6 +20524,9 @@
       <c r="B773" t="s">
         <v>15</v>
       </c>
+      <c r="C773">
+        <v>37095</v>
+      </c>
       <c r="D773" t="s">
         <v>14</v>
       </c>
@@ -20034,6 +20550,9 @@
       <c r="B774" t="s">
         <v>15</v>
       </c>
+      <c r="C774">
+        <v>74801</v>
+      </c>
       <c r="D774" t="s">
         <v>14</v>
       </c>
@@ -20057,6 +20576,9 @@
       <c r="B775" t="s">
         <v>15</v>
       </c>
+      <c r="C775">
+        <v>37757</v>
+      </c>
       <c r="D775" t="s">
         <v>14</v>
       </c>
@@ -20080,6 +20602,9 @@
       <c r="B776" t="s">
         <v>15</v>
       </c>
+      <c r="C776">
+        <v>50038</v>
+      </c>
       <c r="D776" t="s">
         <v>14</v>
       </c>
@@ -20103,6 +20628,9 @@
       <c r="B777" t="s">
         <v>15</v>
       </c>
+      <c r="C777">
+        <v>23750</v>
+      </c>
       <c r="D777" t="s">
         <v>14</v>
       </c>
@@ -20126,6 +20654,9 @@
       <c r="B778" t="s">
         <v>15</v>
       </c>
+      <c r="C778">
+        <v>86400</v>
+      </c>
       <c r="D778" t="s">
         <v>14</v>
       </c>
@@ -20149,6 +20680,9 @@
       <c r="B779" t="s">
         <v>15</v>
       </c>
+      <c r="C779">
+        <v>86400</v>
+      </c>
       <c r="D779" t="s">
         <v>14</v>
       </c>
@@ -20172,6 +20706,9 @@
       <c r="B780" t="s">
         <v>15</v>
       </c>
+      <c r="C780">
+        <v>36391</v>
+      </c>
       <c r="D780" t="s">
         <v>14</v>
       </c>
@@ -20195,6 +20732,9 @@
       <c r="B781" t="s">
         <v>15</v>
       </c>
+      <c r="C781">
+        <v>64251</v>
+      </c>
       <c r="D781" t="s">
         <v>14</v>
       </c>
@@ -20218,6 +20758,9 @@
       <c r="B782" t="s">
         <v>15</v>
       </c>
+      <c r="C782">
+        <v>86400</v>
+      </c>
       <c r="D782" t="s">
         <v>14</v>
       </c>
@@ -20241,6 +20784,9 @@
       <c r="B783" t="s">
         <v>15</v>
       </c>
+      <c r="C783">
+        <v>53476</v>
+      </c>
       <c r="D783" t="s">
         <v>14</v>
       </c>
@@ -20264,6 +20810,9 @@
       <c r="B784" t="s">
         <v>15</v>
       </c>
+      <c r="C784">
+        <v>25874</v>
+      </c>
       <c r="D784" t="s">
         <v>14</v>
       </c>
@@ -20287,6 +20836,9 @@
       <c r="B785" t="s">
         <v>15</v>
       </c>
+      <c r="C785">
+        <v>78489</v>
+      </c>
       <c r="D785" t="s">
         <v>14</v>
       </c>
@@ -20310,6 +20862,9 @@
       <c r="B786" t="s">
         <v>15</v>
       </c>
+      <c r="C786">
+        <v>73979</v>
+      </c>
       <c r="D786" t="s">
         <v>14</v>
       </c>
@@ -20333,6 +20888,9 @@
       <c r="B787" t="s">
         <v>15</v>
       </c>
+      <c r="C787">
+        <v>86400</v>
+      </c>
       <c r="D787" t="s">
         <v>14</v>
       </c>
@@ -20356,6 +20914,9 @@
       <c r="B788" t="s">
         <v>15</v>
       </c>
+      <c r="C788">
+        <v>57069</v>
+      </c>
       <c r="D788" t="s">
         <v>14</v>
       </c>
@@ -20379,6 +20940,9 @@
       <c r="B789" t="s">
         <v>15</v>
       </c>
+      <c r="C789">
+        <v>29866</v>
+      </c>
       <c r="D789" t="s">
         <v>14</v>
       </c>
@@ -20402,6 +20966,9 @@
       <c r="B790" t="s">
         <v>15</v>
       </c>
+      <c r="C790">
+        <v>42467</v>
+      </c>
       <c r="D790" t="s">
         <v>14</v>
       </c>
@@ -20425,6 +20992,9 @@
       <c r="B791" t="s">
         <v>15</v>
       </c>
+      <c r="C791">
+        <v>82097</v>
+      </c>
       <c r="D791" t="s">
         <v>14</v>
       </c>
@@ -20448,6 +21018,9 @@
       <c r="B792" t="s">
         <v>15</v>
       </c>
+      <c r="C792">
+        <v>27486</v>
+      </c>
       <c r="D792" t="s">
         <v>14</v>
       </c>
@@ -20471,6 +21044,9 @@
       <c r="B793" t="s">
         <v>15</v>
       </c>
+      <c r="C793">
+        <v>53809</v>
+      </c>
       <c r="D793" t="s">
         <v>14</v>
       </c>
@@ -20494,6 +21070,9 @@
       <c r="B794" t="s">
         <v>15</v>
       </c>
+      <c r="C794">
+        <v>78106</v>
+      </c>
       <c r="D794" t="s">
         <v>14</v>
       </c>
@@ -20517,6 +21096,9 @@
       <c r="B795" t="s">
         <v>15</v>
       </c>
+      <c r="C795">
+        <v>20883</v>
+      </c>
       <c r="D795" t="s">
         <v>14</v>
       </c>
@@ -20530,6 +21112,162 @@
         <v>1</v>
       </c>
       <c r="I795" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="796" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A796" s="1">
+        <v>794</v>
+      </c>
+      <c r="B796" t="s">
+        <v>15</v>
+      </c>
+      <c r="C796">
+        <v>26449</v>
+      </c>
+      <c r="D796" t="s">
+        <v>14</v>
+      </c>
+      <c r="F796" t="b">
+        <v>1</v>
+      </c>
+      <c r="G796" t="b">
+        <v>1</v>
+      </c>
+      <c r="H796" t="b">
+        <v>1</v>
+      </c>
+      <c r="I796" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="797" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A797" s="1">
+        <v>795</v>
+      </c>
+      <c r="B797" t="s">
+        <v>15</v>
+      </c>
+      <c r="C797">
+        <v>17196</v>
+      </c>
+      <c r="D797" t="s">
+        <v>14</v>
+      </c>
+      <c r="F797" t="b">
+        <v>1</v>
+      </c>
+      <c r="G797" t="b">
+        <v>1</v>
+      </c>
+      <c r="H797" t="b">
+        <v>1</v>
+      </c>
+      <c r="I797" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="798" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A798" s="1">
+        <v>796</v>
+      </c>
+      <c r="B798" t="s">
+        <v>15</v>
+      </c>
+      <c r="C798">
+        <v>46726</v>
+      </c>
+      <c r="D798" t="s">
+        <v>14</v>
+      </c>
+      <c r="F798" t="b">
+        <v>1</v>
+      </c>
+      <c r="G798" t="b">
+        <v>1</v>
+      </c>
+      <c r="H798" t="b">
+        <v>1</v>
+      </c>
+      <c r="I798" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="799" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A799" s="1">
+        <v>797</v>
+      </c>
+      <c r="B799" t="s">
+        <v>15</v>
+      </c>
+      <c r="C799">
+        <v>43138</v>
+      </c>
+      <c r="D799" t="s">
+        <v>14</v>
+      </c>
+      <c r="F799" t="b">
+        <v>1</v>
+      </c>
+      <c r="G799" t="b">
+        <v>1</v>
+      </c>
+      <c r="H799" t="b">
+        <v>1</v>
+      </c>
+      <c r="I799" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="800" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A800" s="1">
+        <v>798</v>
+      </c>
+      <c r="B800" t="s">
+        <v>15</v>
+      </c>
+      <c r="C800">
+        <v>26322</v>
+      </c>
+      <c r="D800" t="s">
+        <v>14</v>
+      </c>
+      <c r="F800" t="b">
+        <v>1</v>
+      </c>
+      <c r="G800" t="b">
+        <v>1</v>
+      </c>
+      <c r="H800" t="b">
+        <v>1</v>
+      </c>
+      <c r="I800" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="801" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A801" s="1">
+        <v>799</v>
+      </c>
+      <c r="B801" t="s">
+        <v>15</v>
+      </c>
+      <c r="C801">
+        <v>27136</v>
+      </c>
+      <c r="D801" t="s">
+        <v>14</v>
+      </c>
+      <c r="F801" t="b">
+        <v>1</v>
+      </c>
+      <c r="G801" t="b">
+        <v>1</v>
+      </c>
+      <c r="H801" t="b">
+        <v>1</v>
+      </c>
+      <c r="I801" t="b">
         <v>0</v>
       </c>
     </row>
